--- a/data/trans_dic/IP31KM12_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM12_2023-Habitat-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>94,79; 99,42</t>
+          <t>98,35; 100,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>98,41; 100,0</t>
+          <t>95,03; 99,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97,49; 99,58</t>
+          <t>97,26; 99,6</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>94,13; 98,75</t>
+          <t>96,73; 99,56</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>96,82; 99,57</t>
+          <t>93,98; 98,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>96,56; 98,86</t>
+          <t>96,34; 98,89</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,89%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>96,76; 99,65</t>
+          <t>96,8; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>97,14; 100,0</t>
+          <t>95,46; 99,47</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>97,83; 99,7</t>
+          <t>97,41; 99,67</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,99%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>91,58; 97,58</t>
+          <t>95,79; 100,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>96,45; 100,0</t>
+          <t>91,27; 97,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94,98; 98,3</t>
+          <t>94,96; 98,4</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,09%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>95,96; 98,23</t>
+          <t>98,26; 99,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>98,26; 99,56</t>
+          <t>95,71; 97,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>97,49; 98,75</t>
+          <t>97,31; 98,67</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>184</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>111862</t>
+          <t>122555</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>136396</t>
+          <t>116083</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>248259</t>
+          <t>238637</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>108301; 113586</t>
+          <t>120863; 122896</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>134645; 136815</t>
+          <t>112706; 117854</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>244764; 250013</t>
+          <t>234888; 240521</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>261</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>180484</t>
+          <t>228322</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>244284</t>
+          <t>174938</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>424768</t>
+          <t>403259</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>175181; 183793</t>
+          <t>223674; 230226</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>239637; 246449</t>
+          <t>169723; 178193</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>418718; 428685</t>
+          <t>396779; 407244</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>185813</t>
+          <t>165551</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>182050</t>
+          <t>152443</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>367864</t>
+          <t>317995</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>182150; 187582</t>
+          <t>161198; 166522</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>177859; 183089</t>
+          <t>148002; 154223</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>363298; 370226</t>
+          <t>313238; 320513</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>224</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>156525</t>
+          <t>164138</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>175272</t>
+          <t>156081</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>331797</t>
+          <t>320218</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>150673; 160544</t>
+          <t>159166; 166165</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>171011; 177309</t>
+          <t>149671; 160053</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>324684; 336033</t>
+          <t>313514; 324846</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>888</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>931</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>634685</t>
+          <t>680565</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>738002</t>
+          <t>599545</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1372687</t>
+          <t>1280109</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>626735; 641562</t>
+          <t>674888; 684044</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>731772; 741486</t>
+          <t>591684; 605462</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1362794; 1380432</t>
+          <t>1269948; 1287702</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP31KM12_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM12_2023-Habitat-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Menores que desayunan todos los días (tasa de respuesta: 100,0%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>&lt;10.000 hab</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>99,72%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>97,88%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>98,35; 100,0</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>95,03; 99,37</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>97,26; 99,6</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>10-50.000 hab</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>98,74%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>96,87%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>97,92%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>96,73; 99,56</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>93,98; 98,67</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>96,34; 98,89</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>99,42%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>98,33%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>98,89%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>96,8; 100,0</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>95,46; 99,47</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>97,41; 99,67</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Capitales</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>98,78%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>95,18%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>96,99%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>95,79; 100,0</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>91,27; 97,61</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>94,96; 98,4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>96,98%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>98,09%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>98,26; 99,6</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>95,71; 97,94</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>97,31; 98,67</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>347</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.9972212533766794</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.9787927088370383</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.9881709978878601</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>122555</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>116083</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>238637</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0.9834543963342025</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.9503165224999156</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.9726444139576658</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>120863; 122896</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>112706; 117854</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>234888; 240521</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.9937263119227029</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.9959690332488548</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>580</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.9873759725936623</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.9686876371165243</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.9791809609759611</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>228322</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>174938</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>403259</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.9672746253050523</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.9398114818714466</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.9634462986060767</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>223674; 230226</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>169723; 178193</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>396779; 407244</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.9956093376807386</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.986710766666043</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.9888574095763705</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>438</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.9941703743079514</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.9832647155695005</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.9889122776391666</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>165551</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>152443</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>317995</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.9680302951529794</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.9546179237829037</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.9741186160359151</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>161198; 166522</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>148002; 154223</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>313238; 320513</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.9947427015948328</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.996744829325847</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>454</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.987799880197569</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.951832915539555</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.9699354715029186</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>164138</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>156081</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>320218</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.9578799738831649</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.9127459674425713</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.9496291979840965</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>159166; 166165</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>149671; 160053</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>313514; 324846</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.9760565328469158</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9839538016604785</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>931</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>888</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1819</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.9908875051379264</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.9698112443779168</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.9809034490817417</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>680565</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>599545</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1280109</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.9826209889953467</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.9570958060483092</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.9731174152426754</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>674888; 684044</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>591684; 605462</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>1269948; 1287702</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.9959517066210481</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.979381608515451</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.9867210053714085</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que desayunan todos los días (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>163</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>184</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>122555</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>116083</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>238637</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>120863</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>112706</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>234888</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>122896</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>117854</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>240521</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>319</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>261</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>228322</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>174938</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>403259</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>223674</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>169723</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>396779</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>230226</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>178193</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>407244</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>219</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>219</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>165551</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>152443</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>317995</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>161198</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>148002</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>313238</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>166522</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>154223</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>320513</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>230</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>224</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>164138</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>156081</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>320218</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>159166</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>149671</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>313514</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>166165</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>160053</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>324846</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>931</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>888</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>680565</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>599545</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1280109</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>674888</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>591684</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>1269948</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>684044</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>605462</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1287702</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>